--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -451,14 +451,10 @@
           <t>超声电子</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>风华高科</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
@@ -468,11 +464,7 @@
           <t>风华高科</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>超声电子</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>风华高科</t>
@@ -482,34 +474,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>华胜天成</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>金安国纪</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>九鼎新材</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>华胜天成</t>
-        </is>
-      </c>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
@@ -519,82 +503,62 @@
           <t>远东股份</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>博敏电子</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>华胜天成</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>远东股份</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>金安国纪</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>双星新材</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>内蒙一机</t>
-        </is>
-      </c>
+          <t>博敏电子</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>博敏电子</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>双星新材</t>
-        </is>
-      </c>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>博敏电子</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>金安国纪</t>
-        </is>
-      </c>
+          <t>九鼎新材</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
@@ -604,45 +568,33 @@
           <t>内蒙一机</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>光电股份</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>双星新材</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>崇达技术</t>
-        </is>
-      </c>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>九鼎新材</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中国巨石</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>铭普光磁</t>
-        </is>
-      </c>
+          <t>崇达技术</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>众泰汽车</t>
@@ -655,48 +607,36 @@
           <t>众泰汽车</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>通达股份</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>崇达技术</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>东方财富</t>
-        </is>
-      </c>
+          <t>铭普光磁</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>内蒙一机</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>闽东电力</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>银河电子</t>
-        </is>
-      </c>
+          <t>中新赛克</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中百集团</t>
+          <t>崇达技术</t>
         </is>
       </c>
     </row>
@@ -706,82 +646,62 @@
           <t>中际旭创</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>众泰汽车</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>博敏电子</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>山子高科</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>闽东电力</t>
-        </is>
-      </c>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>鼎信通讯</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C电科思</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>铜峰电子</t>
-        </is>
-      </c>
+          <t>光电股份</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>内蒙一机</t>
+          <t>中新赛克</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>光电股份</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>博云新材</t>
-        </is>
-      </c>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>长飞光纤</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>国芳集团</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>宇树科技-W</t>
-        </is>
-      </c>
+          <t>剑桥科技</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>博云新材</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,23 +448,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>超声电子</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>风华高科</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>风华高科</t>
@@ -474,104 +482,136 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>华胜天成</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>双星新材</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>远东股份</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>黄河旋风</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>金安国纪</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>杭电股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>博敏电子</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>莲花控股</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>博敏电子</t>
+          <t>桂林旅游</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>山子高科</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>莲花控股</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>风华高科</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>莲花控股</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>内蒙一机</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>中京电子</t>
         </is>
       </c>
     </row>
@@ -581,127 +621,167 @@
           <t>闽东电力</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>康达新材</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>崇达技术</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>豫能控股</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>远东股份</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>中百集团</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>铭普光磁</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>杭电股份</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>通达股份</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>内蒙一机</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>中新赛克</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>豫能控股</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>康达新材</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>天通股份</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>新易盛</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>通达股份</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>光电股份</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>百大集团</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>众泰汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>天通股份</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>贤丰控股</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>博云新材</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,46 +448,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>双星新材</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>双星新材</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,289 +499,289 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>诺德股份</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>诺德股份</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>天顺风能</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>双星新材</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>西陇科学</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>天融信</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>通鼎互联</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>康达新材</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>中京电子</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>天顺风能</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>远东股份</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>桂林旅游</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>中百集团</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>通达股份</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>黄河旋风</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>黄河旋风</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>杭电股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>康达新材</t>
+          <t>风华高科</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>中闽能源</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>金安国纪</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>通达股份</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>浙江众成</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>天融信</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>生益科技</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>众泰汽车</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>中百集团</t>
+          <t>西陇科学</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>赛力斯</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>华正新材</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>众泰汽车</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>生益科技</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,36 +458,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>通鼎互联</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>有研新材</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>永鼎股份</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>闽东电力</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>有研新材</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,131 +499,131 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>永鼎股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t>西陇科学</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>西陇科学</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -635,153 +635,153 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>中晶科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>立昂微</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>宁德时代</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>欣旺达</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>中京电子</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>大为股份</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>黄河旋风</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>青山纸业</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>东材科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>双星新材</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>启明信息</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>浙江众成</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>生益科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>启明信息</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>双星新材</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>生益科技</t>
+          <t>东山精密</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,153 +448,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>N沈鼓</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>京东方A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>众泰汽车</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>桂林旅游</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>中京电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>N沈鼓</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
@@ -606,131 +606,131 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>众泰汽车</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>敦煌种业</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>西陇科学</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>中晶科技</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>立昂微</t>
+          <t>均胜电子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>永鼎股份</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>有研硅</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>欣旺达</t>
+          <t>跨境通</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>通鼎互联</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>青山纸业</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>中天科技</t>
         </is>
       </c>
     </row>
@@ -742,46 +742,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>中晶科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,75 +448,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>C沈鼓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N沈鼓</t>
+          <t>C沈鼓</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>闽东电力</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>金健米业</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>京东方A</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -526,70 +526,70 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>永鼎股份</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N沈鼓</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -601,187 +601,187 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>山子高科</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>敦煌种业</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>长电科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>桂林旅游</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>国瓷材料</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>均胜电子</t>
+          <t>托伦斯</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>京东方A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>C信诺维</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>山子高科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>中天科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>中晶科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>中京电子</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>托伦斯</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>中材科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>顺络电子</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C沈鼓</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -465,267 +465,267 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>华天科技</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>华天科技</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>C沈鼓</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>华胜天成</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>华软科技</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>长电科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>国瓷材料</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>京东方A</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C信诺维</t>
+          <t>诚邦股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>华盛昌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>福龙马</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>锡华科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -737,46 +737,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>华胜天成</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>京东方A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>顺络电子</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>中电鑫龙</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>华天科技</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C沈鼓</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,12 +465,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>华天科技</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,12 +482,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>风华高科</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>风华高科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,58 +499,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C沈鼓</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>中钨高新</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -560,48 +560,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>华胜天成</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -611,48 +611,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>三环集团</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>诚邦股份</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>华软科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>特发信息</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>锡华科技</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>长电科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -662,24 +662,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>长电科技</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>诚邦股份</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
@@ -696,92 +696,92 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>C沈鼓</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>中电鑫龙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>长鑫科技</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>共进股份</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>京东方A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>诚邦股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中电鑫龙</t>
+          <t>红星发展</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>龙头股份</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -451,65 +451,49 @@
           <t>新华传媒</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>华天科技</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>华天科技</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>风华高科</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>风华高科</t>
-        </is>
-      </c>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华软科技</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>华软科技</t>
-        </is>
-      </c>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
@@ -519,269 +503,205 @@
           <t>华瓷股份</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>东方财富</t>
-        </is>
-      </c>
+          <t>中材科技</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中钨高新</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>金健米业</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
+          <t>万  科Ａ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>中材科技</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>锡华科技</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>金健米业</t>
-        </is>
-      </c>
+          <t>新华制药</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>内蒙新华</t>
-        </is>
-      </c>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>三环集团</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>诚邦股份</t>
-        </is>
-      </c>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>华胜天成</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>东方财富</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>特发信息</t>
-        </is>
-      </c>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>双星新材</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>龙头股份</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>锡华科技</t>
-        </is>
-      </c>
+          <t>远东股份</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>新华制药</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>龙头股份</t>
-        </is>
-      </c>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>福龙马</t>
-        </is>
-      </c>
+          <t>京东方Ａ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>南华生物</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>共进股份</t>
-        </is>
-      </c>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>胜宏科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C沈鼓</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>中电鑫龙</t>
-        </is>
-      </c>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>百花医药</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>共进股份</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>长鑫科技</t>
-        </is>
-      </c>
+          <t>华胜天成</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>诚邦股份</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>红星发展</t>
-        </is>
-      </c>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,23 +448,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>中国长城</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N中塑</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>金健米业</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>华天科技</t>
@@ -474,13 +482,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>哈药股份</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>中国长城</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
@@ -490,218 +502,270 @@
           <t>华天科技</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>中国长城</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>中材科技</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>百花医药</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>通富微电</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>双星新材</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>新华制药</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>华天科技</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>百花医药</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>N中塑</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N世纪</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>蓝色光标</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>东山精密</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>风华高科</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>智度股份</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>双星新材</t>
+          <t>中天科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>远东股份</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新华制药</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>国芳集团</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>万科A</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>新华制药</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>新华制药</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>超声电子</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>旋极信息</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>贤丰控股</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>通鼎互联</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>南华生物</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>旋极信息</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>我爱我家</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>引力传媒</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>华胜天成</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中国出版</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>新华制药</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>龙头股份</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>二六三</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>莲花控股</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中国长城</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N中塑</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,302 +470,318 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中国长城</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>莲花控股</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中国长城</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>会稽山</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>C中塑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>京东方Ａ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>京东方A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N中塑</t>
+          <t>C中塑</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N世纪</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>中塑股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>中一科技</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>中一科技</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>凯达重工</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>胜利精密</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>我爱我家</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>智度股份</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>中天科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>沃格光电</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>大亚圣象</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新华制药</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>新华制药</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>旋极信息</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>旋极信息</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>金螳螂</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>先导基电</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>引力传媒</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>莲花控股</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中国出版</t>
+          <t>华远控股</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新华制药</t>
+          <t>先导基电</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>鼎阳科技</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>二六三</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,53 +470,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>雷科防务</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>康强电子</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -526,223 +526,223 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>先导基电</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>会稽山</t>
+          <t>南华生物</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C中塑</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>京东方Ａ</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>京东方A</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C中塑</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中塑股份</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>中一科技</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中一科技</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>凯达重工</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>胜利精密</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>百花医药</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>大亚圣象</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>依顿电子</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>依顿电子</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>漳州发展</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>会稽山</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>金螳螂</t>
+          <t>中京电子</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -754,34 +754,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>鼎阳科技</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>华远控股</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>万向德农</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>鼎阳科技</t>
+          <t>云煤能源</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>云煤能源</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>莲花控股</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,14 +458,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,48 +475,48 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>雷科防务</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>康强电子</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -526,262 +526,262 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>海峡创新</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>哈药股份</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>先导基电</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>内蒙新华</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>福建水泥</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>松发股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>吉鑫科技</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>漳州发展</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>会稽山</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>奥士康</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新 华 都</t>
+          <t>漳州发展</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>合富中国</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>鼎阳科技</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>东方中科</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>云煤能源</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>云煤能源</t>
+          <t>天威视讯</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>天威视讯</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,340 +448,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>平潭发展</t>
-        </is>
-      </c>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>新赛股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>雷科防务</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>雷科防务</t>
-        </is>
-      </c>
+          <t>平潭发展</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>康强电子</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>沈鼓集团</t>
-        </is>
-      </c>
+          <t>雷科防务</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>康强电子</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>康强电子</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>东方中科</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
+          <t>新赛股份</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>雷科防务</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>合富中国</t>
-        </is>
-      </c>
+          <t>奥佳华</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>电科思仪</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>海峡创新</t>
-        </is>
-      </c>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>合富中国</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>电科思仪</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>福建水泥</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>福建水泥</t>
-        </is>
-      </c>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>先导基电</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>奥佳华</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
+          <t>东方中科</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>海峡创新</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>东方财富</t>
-        </is>
-      </c>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>先导基电</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>内蒙新华</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>奥佳华</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>太极实业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
+          <t>国新健康</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>先导基电</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+          <t>华茂股份</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>东方中科</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>松发股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>超声电子</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>新 华 都</t>
-        </is>
-      </c>
+          <t>海峡创新</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>景旺电子</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>吉鑫科技</t>
-        </is>
-      </c>
+          <t>合富中国</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>华茂股份</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>奥士康</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>漳州发展</t>
-        </is>
-      </c>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>宁波东力</t>
-        </is>
-      </c>
+          <t>行云科技</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>天威视讯</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>崇达技术</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>内蒙新华</t>
-        </is>
-      </c>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>天威视讯</t>
-        </is>
-      </c>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,20 +448,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>均胜电子</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -474,20 +474,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>均胜电子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -513,195 +513,195 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>东方中科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>沃格光电</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>集泰股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>国新健康</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>华茂股份</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>天威视讯</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>先导基电</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>行云科技</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>华茂股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>天威视讯</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>京东方A</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,260 +448,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>均胜电子</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>康强电子</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>巨力索具</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>会稽山</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>奥佳华</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>吉鑫科技</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>吉鑫科技</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>跨境通</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>跨境通</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>跨境通</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>康强电子</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均胜电子</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>巨力索具</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>东方中科</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>平潭发展</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>平潭发展</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>雷科防务</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>会稽山</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>彩虹股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>彩虹股份</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>彩虹股份</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>沃格光电</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>巨力索具</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>先导基电</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>会稽山</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>集泰股份</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>合富中国</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>大业股份</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>大业股份</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>福建水泥</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>金辰股份</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>博纳影业</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>众泰汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>上工申贝</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>金辰股份</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>华茂股份</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>金辰股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>雪龙集团</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>宏柏新材</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>海峡创新</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>浙江新能</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>新 华 都</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>雪龙集团</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>有研新材</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>天威视讯</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>雪龙集团</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>京东方A</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,131 +448,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>会稽山</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>N鸿富诚</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>国轩高科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>广汽集团</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>会稽山</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>彩虹股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>彩虹股份</t>
+          <t>广汽集团</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>彩虹股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -594,194 +594,194 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>N鸿富诚</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>深物业A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>亨通光电</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>会稽山</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>雪龙集团</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>滨江集团</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>中新赛克</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>力勤资源</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>信达地产</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>滨江集团</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>金龙羽</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>信达地产</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -465,92 +465,92 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>N力勤</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>N力勤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>力勤资源</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N鸿富诚</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>广汽集团</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -560,228 +560,228 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>广汽集团</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>陆家嘴</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N鸿富诚</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>滨江集团</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>力勤资源</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>信达地产</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>古越龙山</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>近岸蛋白</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>陆家嘴</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>美诺华</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>滨江集团</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金龙羽</t>
+          <t>金徽酒</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>信达地产</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>南华生物</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>传艺科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>国轩高科</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,31 +448,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>万  科Ａ</t>
-        </is>
-      </c>
+          <t>N力勤</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>万科A</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N力勤</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>N力勤</t>
-        </is>
-      </c>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>力勤资源</t>
@@ -482,14 +474,10 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>深物业A</t>
-        </is>
-      </c>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>襄阳轴承</t>
@@ -499,31 +487,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>我爱我家</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>襄阳轴承</t>
-        </is>
-      </c>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>新华传媒</t>
@@ -533,255 +513,195 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
+          <t>万  科Ａ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>深物业A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>赛力斯</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>大金重工</t>
-        </is>
-      </c>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>陆家嘴</t>
-        </is>
-      </c>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>亨通光电</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>我爱我家</t>
-        </is>
-      </c>
+          <t>国轩高科</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>昭衍新药</t>
-        </is>
-      </c>
+          <t>深物业A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>哈药股份</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>美诺华</t>
-        </is>
-      </c>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>美诺华</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>善水科技</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>古越龙山</t>
-        </is>
-      </c>
+          <t>行云科技</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>近岸蛋白</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>陆家嘴</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>龙蟠科技</t>
-        </is>
-      </c>
+          <t>掌阅科技</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>国轩高科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>金健米业</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>传艺科技</t>
-        </is>
-      </c>
+          <t>中文在线</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金徽酒</t>
-        </is>
-      </c>
+          <t>华策影视</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>传艺科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>南华生物</t>
-        </is>
-      </c>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>平潭发展</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
+          <t>浙文影业</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,10 +448,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N力勤</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>九阳股份</t>
@@ -461,10 +465,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>万  科Ａ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N力勤</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>力勤资源</t>
@@ -474,10 +482,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>襄阳轴承</t>
@@ -487,10 +499,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>N力勤</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>大金重工</t>
@@ -500,10 +516,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>赛力斯</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>万  科Ａ</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>新华传媒</t>
@@ -513,195 +533,255 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>万科A</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>江淮汽车</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>万科A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>宇树科技-W</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>国轩高科</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>昭衍新药</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>赛力斯</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>深物业A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>深物业A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>传艺科技</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>东方财富</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>国轩高科</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>深物业A</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>美诺华</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>行云科技</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>上海洗霸</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>龙蟠科技</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中文在线</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>美诺华</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>美诺华</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>华策影视</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>行云科技</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>昭衍新药</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中船科技</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>传艺科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>浙文影业</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>五方光电</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>贵州茅台</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,340 +448,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N力勤</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>力勤资源</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N力勤</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>圣阳股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>东山精密</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>C力勤</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>万科A</t>
+          <t>金牛化工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>C力勤</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>传艺科技</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>紫竹高科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>力勤资源</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>行云科技</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中船科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>赛力斯</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>五方光电</t>
+          <t>紫竹高科</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>山东墨龙</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -451,16 +451,8 @@
           <t>江淮汽车</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -468,67 +460,35 @@
           <t>新华传媒</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>龙蟠科技</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
+          <t>中文在线</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
+          <t>天赐材料</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -536,254 +496,134 @@
           <t>九阳股份</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>传艺科技</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>金健米业</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>雄韬股份</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>东山精密</t>
-        </is>
-      </c>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>传艺科技</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>C力勤</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
+          <t>芒果超媒</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C力勤</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>沈鼓集团</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
+          <t>东岳硅材</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>大金重工</t>
-        </is>
-      </c>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>龙蟠科技</t>
-        </is>
-      </c>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>传艺科技</t>
-        </is>
-      </c>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>丰元股份</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>紫竹高科</t>
-        </is>
-      </c>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
+          <t>中国巨石</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>东山精密</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>顺灏股份</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>力勤资源</t>
-        </is>
-      </c>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>顺灏股份</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>山东墨龙</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>宇树科技</t>
-        </is>
-      </c>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>兴业股份</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>华北制药</t>
-        </is>
-      </c>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>华北制药</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>华北制药</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>襄阳轴承</t>
-        </is>
-      </c>
+          <t>绿盟科技</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>兴业股份</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>赛力斯</t>
-        </is>
-      </c>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>丰元股份</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>紫竹高科</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>山东墨龙</t>
-        </is>
-      </c>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,182 +448,342 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>江淮汽车</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>新华传媒</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>金健米业</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>中文在线</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>中文在线</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>天赐材料</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>天赐材料</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>华北制药</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>大金重工</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+          <t>天赐材料</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天赐材料</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>芒果超媒</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>芒果超媒</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>博纳影业</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+          <t>分众传媒</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>东岳硅材</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>分众传媒</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>分众传媒</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>长鑫科技</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>华北制药</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中国巨石</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>多氟多</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+          <t>绿盟科技</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>丰元股份</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>东方财富</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>东岳硅材</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>博纳影业</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>掌阅科技</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中文在线</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>天融信</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,24 +448,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>赛力斯</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>赛力斯</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>赛力斯</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,36 +475,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -516,272 +516,272 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>博纳影业</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>分众传媒</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>天顺风能</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>分众传媒</t>
+          <t>东百集团</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>分众传媒</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>龙版传媒</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>多氟多</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>远程股份</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>远程股份</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>吉视传媒</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>启明星辰</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>掌阅科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>天顺风能</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>新经典</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>天融信</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>联讯仪器</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>远程股份</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,63 +448,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赛力斯</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>N粤芯-U</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>龙版传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -516,46 +516,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>东百集团</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>东百集团</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -567,199 +567,199 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>富春染织</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>N粤芯-U</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>粤桂股份</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>粤桂股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>吉华集团</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>果麦文化</t>
+          <t>粤桂股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>远程股份</t>
+          <t>凯美特气</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>富春染织</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>远程股份</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>新 华 都</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>启明星辰</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>长白山</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>德才股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>粤芯半导体</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -771,17 +771,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>亚邦股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>联讯仪器</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>远程股份</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,165 +448,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>龙版传媒</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N粤芯-U</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>富春股份</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>东百集团</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>富春股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>掌阅科技</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>富春染织</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>C粤芯-U</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N粤芯-U</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -618,170 +618,170 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>引力传媒</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>粤桂股份</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>中文在线</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>郑州煤电</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>慈文传媒</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>慈文传媒</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>丽人丽妆</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>粤桂股份</t>
+          <t>新经典</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>七 匹 狼</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>吉华集团</t>
+          <t>C粤芯-U</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>粤桂股份</t>
+          <t>韶能股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>中文在线</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>凯美特气</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>富春染织</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>丽人丽妆</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>电魂网络</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>粤芯半导体</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>长白山</t>
+          <t>新经典</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>兴森科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>宝鼎科技</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>粤芯半导体</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>芒果超媒</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>中国科传</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新经典</t>
+          <t>金安国纪</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>亚邦股份</t>
+          <t>郑州煤电</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>丽人丽妆</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,46 +448,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>N联亚</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富春股份</t>
+          <t>华林证券</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,279 +499,279 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>富春股份</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>N联亚</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>东百集团</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>超声电子</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C粤芯-U</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>引力传媒</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>掌阅科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>新经典</t>
+          <t>华林证券</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>七 匹 狼</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C粤芯-U</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>电魂网络</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>粤芯半导体</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新经典</t>
+          <t>至纯科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>联亚药业</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>宝鼎科技</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>龙版传媒</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>丽人丽妆</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中国科传</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,238 +448,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N联亚</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>华林证券</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N联亚</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>杭电股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>东百集团</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>皇台酒业</t>
+          <t>金盾股份</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>中信海直</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>长鑫科技</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>掌阅科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>华林证券</t>
+          <t>杭电股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>华力创通</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中信海直</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>杭电股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
@@ -691,97 +691,97 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>皇台酒业</t>
+          <t>金盾股份</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>至纯科技</t>
+          <t>均胜电子</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>联亚药业</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>晨曦航空</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>阳光乳业</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>捷众科技</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>大金重工</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>中信海直</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,12 +482,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,24 +499,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>万丰奥威</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -526,167 +526,167 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>中信海直</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>金盾股份</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>华力创通</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -696,92 +696,92 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>宗申动力</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>尖峰集团</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>长城军工</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>恒瑞医药</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>上工申贝</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>药明康德</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>均胜电子</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>晨曦航空</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>平安银行</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>捷众科技</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>尖峰集团</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>捷众科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -458,14 +458,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>万丰奥威</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,14 +475,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>保隆科技</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -504,284 +504,284 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>长城军工</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>中信海直</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>ST绝味</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>宗申动力</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>金盾股份</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>金盾股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金奥博</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>金奥博</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>中信海直</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>金盾股份</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>尖峰集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>恒瑞医药</t>
+          <t>晨曦航空</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>华力创通</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>上工申贝</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>平安银行</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>读者传媒</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>金奥博</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>尖峰集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>捷众科技</t>
+          <t>甘化科工</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,17 +448,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
@@ -470,318 +470,318 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ST绝味</t>
+          <t>万丰奥威</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金盾股份</t>
+          <t>甘化科工</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>金盾股份</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>东安动力</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>大业股份</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>海洋王</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>晶科科技</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>晨曦航空</t>
+          <t>甘化科工</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>长城军工</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>德明利</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>海洋王</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>华力创通</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>读者传媒</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>保隆科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>甘化科工</t>
+          <t>沃特股份</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,24 +448,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,155 +475,155 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>长盈精密</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>长盈精密</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>万丰奥威</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>长鑫科技</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>澳弘电子</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>澳弘电子</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>澳弘电子</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -635,153 +635,153 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>甘化科工</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>晶科科技</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>甘化科工</t>
+          <t>索辰科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>粤 传 媒</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>奥比中光-W</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>海洋王</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>中国巨石</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>能科科技</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>沃特股份</t>
+          <t>科森科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>东安动力</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -453,29 +453,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>宁德时代</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
@@ -487,19 +487,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>长盈精密</t>
+          <t>太极股份</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -509,160 +509,160 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>长盈精密</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>粤 传 媒</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>云南锗业</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>云南锗业</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>利通电子</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>利通电子</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>粤 传 媒</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>利通电子</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>远东股份</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
@@ -674,114 +674,114 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>云南锗业</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>东安动力</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>索辰科技</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>粤 传 媒</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>奥比中光-W</t>
+          <t>太极股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>航天信息</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>润建股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>能科科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>科森科技</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,34 +465,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>宁德时代</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>太极股份</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -516,211 +516,211 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>新易盛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>大业股份</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>粤 传 媒</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>云南锗业</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>云南锗业</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>雪人集团</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>粤 传 媒</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>山河智能</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>亨通光电</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>天洋新材</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>绿盟科技</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>云南锗业</t>
+          <t>山河智能</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -730,58 +730,58 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>东安动力</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>太极股份</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>航天信息</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>杰瑞股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>星光股份</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>三峡新材</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -453,19 +453,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>宇树科技-W</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>华天科技</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>宁德时代</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,65 +475,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -543,245 +543,245 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>天娱数科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>宁德时代</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>三峡新材</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>襄阳轴承</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>大洋电机</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>山河智能</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>粤芯半导-U</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>歌尔股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天洋新材</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>新易盛</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>山河智能</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>大洋电机</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>有研新材</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>杰瑞股份</t>
+          <t>海天瑞声</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>星光股份</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>华林证券</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,182 +448,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>天娱数科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>东岳硅材</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>凡拓数创</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>歌尔股份</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>凡拓数创</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>赣锋锂业</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>能科科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>利亚德</t>
         </is>
       </c>
     </row>
@@ -657,131 +657,131 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>粤芯半导-U</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>风华高科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>歌尔股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>宁德时代</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>歌尔股份</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>达实智能</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>风语筑</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>赣锋锂业</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>榕基软件</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>奥比中光-W</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>埃斯顿</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>海天瑞声</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>华林证券</t>
+          <t>三峡新材</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -453,29 +453,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
@@ -492,65 +492,65 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>天娱数科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>宇树科技-W</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>利亚德</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>宇树科技-W</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -560,41 +560,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>歌尔股份</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>凡拓数创</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
@@ -606,182 +606,182 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>赣锋锂业</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>能科科技</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>赛福天</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>能科科技</t>
+          <t>达实智能</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>埃斯顿</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>达实智能</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>达实智能</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>榕基软件</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>利亚德</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>歌尔股份</t>
+          <t>能科科技</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>达实智能</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>兆威机电</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>赣锋锂业</t>
+          <t>榕基软件</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>榕基软件</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>奥比中光-W</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>风语筑</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>天奇股份</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>高争民爆</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,233 +482,233 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>中国石油</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>中国石油</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>上纬新材</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>天娱数科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>能科科技</t>
+          <t>模塑科技</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>达实智能</t>
+          <t>大西洋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>万向钱潮</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>东方海洋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>达实智能</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>达实智能</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>大西洋</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>榕基软件</t>
+          <t>创维数字</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>赛福天</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>能科科技</t>
+          <t>上纬新材</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>锋龙股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -720,68 +720,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>东方财富</t>
+          <t>模塑科技</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>中国石油</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>榕基软件</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>林州重机</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>林州重机</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>海量数据</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>福莱新材</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>风语筑</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>天奇股份</t>
+          <t>林州重机</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>高争民爆</t>
+          <t>三羊马</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,85 +448,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>大洋电机</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
@@ -538,24 +538,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中国石油</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -567,221 +567,221 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>中国石油</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>上纬新材</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>大西洋</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>广百股份</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>国芳集团</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>茂业商业</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>天娱数科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>大西洋</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>创维数字</t>
+          <t>百大集团</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>新华百货</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>上纬新材</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>锋龙股份</t>
+          <t>桂发祥</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>赛福天</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中国石油</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>亚太股份</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t>光洋股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t>广百股份</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>沪光股份</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>金安国纪</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>百大集团</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t>深 赛 格</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>德明利</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,63 +482,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>万向钱潮</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>光洋股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -550,153 +550,153 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>大洋电机</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>方正科技</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>华天科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新华百货</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>雪人集团</t>
+          <t>方正科技</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>广百股份</t>
+          <t>君正股份</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>茂业商业</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>澳洋健康</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新华百货</t>
+          <t>东贝集团</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>文投控股</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新华百货</t>
+          <t>金安国纪</t>
         </is>
       </c>
     </row>
@@ -708,80 +708,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>桂发祥</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>东贝集团</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>东贝集团</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>福莱新材</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>文投控股</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>亚太股份</t>
+          <t>山东矿机</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>兆易创新</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>广百股份</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>沪光股份</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>君正股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>深 赛 格</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>五洲新春</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,340 +448,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>中国卫星</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>天孚通信</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>中国卫星</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>新易盛</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>阳光照明</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>上海沪工</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>东山精密</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>光洋股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>上海沪工</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>方正科技</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>盛洋科技</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>盛洋科技</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>东方海洋</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>文投控股</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>文投控股</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>盛洋科技</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>方正科技</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>君正股份</t>
+          <t>西部材料</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>上海沪工</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>海洋王</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>澳洋健康</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>澳洋健康</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>东贝集团</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>工商银行</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>东贝集团</t>
+          <t>中国卫星</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>中金公司</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>东贝集团</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>澳洋健康</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>平煤股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>山东矿机</t>
+          <t>航天晨光</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>钧达股份</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>文投控股</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>君正股份</t>
+          <t>山西焦煤</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>一鸣食品</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>大洋电机</t>
         </is>
       </c>
     </row>

--- a/HotStock_Top20.xlsx
+++ b/HotStock_Top20.xlsx
@@ -448,17 +448,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中国卫星</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
@@ -470,24 +470,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中国卫星</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,289 +499,289 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>海洋王</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>东方海洋</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>襄阳轴承</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>东方海洋</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>襄阳轴承</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>东山精密</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>上海沪工</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>中际旭创</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>澳洋健康</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>上海沪工</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>泸州老窖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>金安国纪</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>盛洋科技</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>盛洋科技</t>
+          <t>上海沪工</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>宇树科技</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>盛洋科技</t>
+          <t>阳光照明</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>上海沪工</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>西部材料</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海沪工</t>
+          <t>长鑫科技</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>泸州老窖</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>青岛食品</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>工商银行</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>贵州茅台</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>盛洋科技</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中国卫星</t>
+          <t>青岛食品</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中金公司</t>
+          <t>宇树科技-W</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>盛洋科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>盛洋科技</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>平煤股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>航天晨光</t>
+          <t>青岛食品</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>上海沪工</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>钧达股份</t>
+          <t>*ST闻泰</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>兆易创新</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>山西焦煤</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>一鸣食品</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>哈药股份</t>
         </is>
       </c>
     </row>
